--- a/Scenario Case.xlsx
+++ b/Scenario Case.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="94">
   <si>
     <t/>
   </si>
@@ -185,6 +185,9 @@
     <t>(0,0)</t>
   </si>
   <si>
+    <t>7680x2160</t>
+  </si>
+  <si>
     <t>DP_RGB888</t>
   </si>
   <si>
@@ -200,6 +203,9 @@
     <t>layer0 -- panel0 -- interface0
 layer1 -- panel1 -- inteface0
 layer2 -- panel2 -- inteface0</t>
+  </si>
+  <si>
+    <t>11520x2160</t>
   </si>
   <si>
     <t>12k splice
@@ -227,6 +233,9 @@
 layer1 -- panel1 -- inteface0
 layer2 -- panel2 -- inteface0
 layer3 -- panel3 -- inteface0</t>
+  </si>
+  <si>
+    <t>15360x2160</t>
   </si>
   <si>
     <t>验证中控显示通过滑屏手势移至仪表显示时，跨屏迁移的触控响应时效与画面连续性。（例如导航地图窗口从最左边移到最右边）</t>
@@ -1346,7 +1355,7 @@
         <v>48</v>
       </c>
       <c r="AC4" s="19" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="AD4" s="20" t="s">
         <v>50</v>
@@ -1373,7 +1382,7 @@
         <v>0</v>
       </c>
       <c r="AL4" s="19" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AM4" s="20" t="s">
         <v>50</v>
@@ -1478,7 +1487,7 @@
         <v>0</v>
       </c>
       <c r="AL5" s="19" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AM5" s="20" t="s"/>
     </row>
@@ -1488,14 +1497,14 @@
       </c>
       <c r="B6" s="25" t="s"/>
       <c r="C6" s="27" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D6" s="25" t="s"/>
       <c r="E6" s="17" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F6" s="18" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G6" s="14">
         <v>0</v>
@@ -1564,7 +1573,7 @@
         <v>48</v>
       </c>
       <c r="AC6" s="19" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="AD6" s="20" t="s">
         <v>50</v>
@@ -1591,7 +1600,7 @@
         <v>0</v>
       </c>
       <c r="AL6" s="19" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AM6" s="20" t="s">
         <v>50</v>
@@ -1696,7 +1705,7 @@
         <v>0</v>
       </c>
       <c r="AL7" s="19" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AM7" s="20" t="s"/>
     </row>
@@ -1799,7 +1808,7 @@
         <v>0</v>
       </c>
       <c r="AL8" s="19" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AM8" s="20" t="s"/>
     </row>
@@ -1809,14 +1818,14 @@
       </c>
       <c r="B9" s="25" t="s"/>
       <c r="C9" s="27" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D9" s="25" t="s"/>
       <c r="E9" s="17" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F9" s="18" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G9" s="14">
         <v>0</v>
@@ -1885,7 +1894,7 @@
         <v>48</v>
       </c>
       <c r="AC9" s="19" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="AD9" s="20" t="s">
         <v>51</v>
@@ -1912,7 +1921,7 @@
         <v>1</v>
       </c>
       <c r="AL9" s="19" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AM9" s="20" t="s">
         <v>50</v>
@@ -2017,7 +2026,7 @@
         <v>1</v>
       </c>
       <c r="AL10" s="19" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AM10" s="20" t="s"/>
     </row>
@@ -2120,7 +2129,7 @@
         <v>1</v>
       </c>
       <c r="AL11" s="19" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AM11" s="20" t="s"/>
     </row>
@@ -2130,14 +2139,14 @@
       </c>
       <c r="B12" s="25" t="s"/>
       <c r="C12" s="27" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D12" s="25" t="s"/>
       <c r="E12" s="17" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F12" s="18" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="G12" s="14">
         <v>0</v>
@@ -2206,7 +2215,7 @@
         <v>48</v>
       </c>
       <c r="AC12" s="19" t="s">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="AD12" s="20" t="s">
         <v>51</v>
@@ -2233,7 +2242,7 @@
         <v>0</v>
       </c>
       <c r="AL12" s="19" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AM12" s="20" t="s">
         <v>50</v>
@@ -2338,7 +2347,7 @@
         <v>0</v>
       </c>
       <c r="AL13" s="19" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AM13" s="20" t="s"/>
     </row>
@@ -2441,7 +2450,7 @@
         <v>0</v>
       </c>
       <c r="AL14" s="19" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AM14" s="20" t="s"/>
     </row>
@@ -2544,7 +2553,7 @@
         <v>0</v>
       </c>
       <c r="AL15" s="19" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AM15" s="20" t="s"/>
     </row>
@@ -2553,19 +2562,19 @@
         <v>5</v>
       </c>
       <c r="B16" s="29" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="C16" s="30" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="D16" s="31" t="s">
         <v>44</v>
       </c>
       <c r="E16" s="32" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="F16" s="33" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="G16" s="34">
         <v>0</v>
@@ -2634,7 +2643,7 @@
         <v>48</v>
       </c>
       <c r="AC16" s="34" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="AD16" s="36" t="s">
         <v>51</v>
@@ -2661,7 +2670,7 @@
         <v>0</v>
       </c>
       <c r="AL16" s="34" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AM16" s="36" t="s">
         <v>50</v>
@@ -2766,7 +2775,7 @@
         <v>0</v>
       </c>
       <c r="AL17" s="19" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AM17" s="20" t="s"/>
     </row>
@@ -2869,7 +2878,7 @@
         <v>0</v>
       </c>
       <c r="AL18" s="19" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AM18" s="20" t="s"/>
     </row>
@@ -2921,7 +2930,7 @@
         <v>51</v>
       </c>
       <c r="U19" s="19" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="V19" s="22" t="s">
         <v>51</v>
@@ -2936,7 +2945,7 @@
         <v>54</v>
       </c>
       <c r="Z19" s="19" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="AA19" s="19">
         <v>0</v>
@@ -2972,7 +2981,7 @@
         <v>0</v>
       </c>
       <c r="AL19" s="19" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AM19" s="20" t="s"/>
     </row>
@@ -2983,7 +2992,7 @@
       <c r="D20" s="25" t="s"/>
       <c r="E20" s="25" t="s"/>
       <c r="F20" s="29" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="G20" s="19">
         <v>1</v>
@@ -3052,7 +3061,7 @@
         <v>48</v>
       </c>
       <c r="AC20" s="19" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="AD20" s="20" t="s">
         <v>51</v>
@@ -3079,7 +3088,7 @@
         <v>0</v>
       </c>
       <c r="AL20" s="19" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AM20" s="20" t="s">
         <v>50</v>
@@ -3184,7 +3193,7 @@
         <v>0</v>
       </c>
       <c r="AL21" s="19" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AM21" s="20" t="s"/>
     </row>
@@ -3287,7 +3296,7 @@
         <v>0</v>
       </c>
       <c r="AL22" s="19" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AM22" s="20" t="s"/>
     </row>
@@ -3339,7 +3348,7 @@
         <v>51</v>
       </c>
       <c r="U23" s="19" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="V23" s="22" t="s">
         <v>51</v>
@@ -3351,10 +3360,10 @@
         <v>53</v>
       </c>
       <c r="Y23" s="19" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="Z23" s="19" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="AA23" s="19">
         <v>0</v>
@@ -3390,7 +3399,7 @@
         <v>0</v>
       </c>
       <c r="AL23" s="19" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AM23" s="20" t="s"/>
     </row>
@@ -3401,7 +3410,7 @@
       <c r="D24" s="25" t="s"/>
       <c r="E24" s="25" t="s"/>
       <c r="F24" s="40" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="G24" s="19">
         <v>2</v>
@@ -3470,7 +3479,7 @@
         <v>48</v>
       </c>
       <c r="AC24" s="19" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="AD24" s="20" t="s">
         <v>51</v>
@@ -3497,7 +3506,7 @@
         <v>0</v>
       </c>
       <c r="AL24" s="19" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AM24" s="20" t="s">
         <v>50</v>
@@ -3602,7 +3611,7 @@
         <v>0</v>
       </c>
       <c r="AL25" s="19" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AM25" s="20" t="s"/>
     </row>
@@ -3705,7 +3714,7 @@
         <v>0</v>
       </c>
       <c r="AL26" s="19" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AM26" s="20" t="s"/>
     </row>
@@ -3757,7 +3766,7 @@
         <v>51</v>
       </c>
       <c r="U27" s="19" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="V27" s="22" t="s">
         <v>51</v>
@@ -3769,10 +3778,10 @@
         <v>53</v>
       </c>
       <c r="Y27" s="19" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="Z27" s="19" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="AA27" s="19">
         <v>0</v>
@@ -3808,7 +3817,7 @@
         <v>0</v>
       </c>
       <c r="AL27" s="19" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AM27" s="20" t="s"/>
     </row>
@@ -3819,7 +3828,7 @@
       <c r="D28" s="25" t="s"/>
       <c r="E28" s="25" t="s"/>
       <c r="F28" s="29" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="G28" s="23">
         <v>3</v>
@@ -3887,8 +3896,8 @@
       <c r="AB28" s="23" t="s">
         <v>48</v>
       </c>
-      <c r="AC28" s="23" t="s">
-        <v>52</v>
+      <c r="AC28" s="19" t="s">
+        <v>60</v>
       </c>
       <c r="AD28" s="22" t="s">
         <v>51</v>
@@ -3915,7 +3924,7 @@
         <v>0</v>
       </c>
       <c r="AL28" s="23" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AM28" s="22" t="s">
         <v>50</v>
@@ -4020,7 +4029,7 @@
         <v>0</v>
       </c>
       <c r="AL29" s="19" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AM29" s="20" t="s"/>
     </row>
@@ -4123,7 +4132,7 @@
         <v>0</v>
       </c>
       <c r="AL30" s="19" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AM30" s="20" t="s"/>
     </row>
@@ -4175,7 +4184,7 @@
         <v>51</v>
       </c>
       <c r="U31" s="19" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="V31" s="22" t="s">
         <v>50</v>
@@ -4184,13 +4193,13 @@
         <v>54</v>
       </c>
       <c r="X31" s="19" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="Y31" s="19" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="Z31" s="19" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="AA31" s="19">
         <v>0</v>
@@ -4226,7 +4235,7 @@
         <v>0</v>
       </c>
       <c r="AL31" s="19" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AM31" s="20" t="s"/>
     </row>
@@ -4278,7 +4287,7 @@
         <v>51</v>
       </c>
       <c r="U32" s="19" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="V32" s="22" t="s">
         <v>50</v>
@@ -4287,13 +4296,13 @@
         <v>54</v>
       </c>
       <c r="X32" s="19" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="Y32" s="19" t="s">
         <v>54</v>
       </c>
       <c r="Z32" s="19" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="AA32" s="19">
         <v>1</v>
@@ -4329,7 +4338,7 @@
         <v>0</v>
       </c>
       <c r="AL32" s="19" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AM32" s="20" t="s"/>
     </row>
@@ -4340,7 +4349,7 @@
       <c r="D33" s="25" t="s"/>
       <c r="E33" s="25" t="s"/>
       <c r="F33" s="29" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="G33" s="23">
         <v>4</v>
@@ -4408,8 +4417,8 @@
       <c r="AB33" s="23" t="s">
         <v>48</v>
       </c>
-      <c r="AC33" s="23" t="s">
-        <v>52</v>
+      <c r="AC33" s="19" t="s">
+        <v>60</v>
       </c>
       <c r="AD33" s="22" t="s">
         <v>51</v>
@@ -4436,7 +4445,7 @@
         <v>0</v>
       </c>
       <c r="AL33" s="23" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AM33" s="22" t="s">
         <v>50</v>
@@ -4541,7 +4550,7 @@
         <v>0</v>
       </c>
       <c r="AL34" s="19" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AM34" s="20" t="s"/>
     </row>
@@ -4644,7 +4653,7 @@
         <v>0</v>
       </c>
       <c r="AL35" s="19" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AM35" s="20" t="s"/>
     </row>
@@ -4696,7 +4705,7 @@
         <v>51</v>
       </c>
       <c r="U36" s="19" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="V36" s="22" t="s">
         <v>51</v>
@@ -4711,7 +4720,7 @@
         <v>54</v>
       </c>
       <c r="Z36" s="19" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="AA36" s="19">
         <v>1</v>
@@ -4747,7 +4756,7 @@
         <v>0</v>
       </c>
       <c r="AL36" s="19" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AM36" s="20" t="s"/>
     </row>
@@ -4758,7 +4767,7 @@
       <c r="D37" s="25" t="s"/>
       <c r="E37" s="25" t="s"/>
       <c r="F37" s="40" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="G37" s="19">
         <v>5</v>
@@ -4827,7 +4836,7 @@
         <v>48</v>
       </c>
       <c r="AC37" s="19" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="AD37" s="20" t="s">
         <v>51</v>
@@ -4854,7 +4863,7 @@
         <v>0</v>
       </c>
       <c r="AL37" s="19" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AM37" s="20" t="s">
         <v>50</v>
@@ -4959,7 +4968,7 @@
         <v>0</v>
       </c>
       <c r="AL38" s="19" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AM38" s="20" t="s"/>
     </row>
@@ -5062,7 +5071,7 @@
         <v>0</v>
       </c>
       <c r="AL39" s="19" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AM39" s="20" t="s"/>
     </row>
@@ -5114,7 +5123,7 @@
         <v>51</v>
       </c>
       <c r="U40" s="19" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="V40" s="22" t="s">
         <v>51</v>
@@ -5126,10 +5135,10 @@
         <v>53</v>
       </c>
       <c r="Y40" s="19" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="Z40" s="19" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="AA40" s="19">
         <v>1</v>
@@ -5165,7 +5174,7 @@
         <v>0</v>
       </c>
       <c r="AL40" s="19" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AM40" s="20" t="s"/>
     </row>
@@ -5176,7 +5185,7 @@
       <c r="D41" s="25" t="s"/>
       <c r="E41" s="25" t="s"/>
       <c r="F41" s="40" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="G41" s="28">
         <v>6</v>
@@ -5244,8 +5253,8 @@
       <c r="AB41" s="28" t="s">
         <v>48</v>
       </c>
-      <c r="AC41" s="28" t="s">
-        <v>52</v>
+      <c r="AC41" s="19" t="s">
+        <v>60</v>
       </c>
       <c r="AD41" s="44" t="s">
         <v>51</v>
@@ -5272,7 +5281,7 @@
         <v>0</v>
       </c>
       <c r="AL41" s="28" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AM41" s="44" t="s">
         <v>50</v>
@@ -5377,7 +5386,7 @@
         <v>0</v>
       </c>
       <c r="AL42" s="19" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AM42" s="20" t="s"/>
     </row>
@@ -5480,7 +5489,7 @@
         <v>0</v>
       </c>
       <c r="AL43" s="19" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AM43" s="20" t="s"/>
     </row>
@@ -5532,7 +5541,7 @@
         <v>51</v>
       </c>
       <c r="U44" s="19" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="V44" s="22" t="s">
         <v>51</v>
@@ -5544,10 +5553,10 @@
         <v>53</v>
       </c>
       <c r="Y44" s="19" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="Z44" s="19" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="AA44" s="19">
         <v>1</v>
@@ -5583,7 +5592,7 @@
         <v>0</v>
       </c>
       <c r="AL44" s="19" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AM44" s="20" t="s"/>
     </row>
@@ -5594,7 +5603,7 @@
       <c r="D45" s="25" t="s"/>
       <c r="E45" s="25" t="s"/>
       <c r="F45" s="29" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="G45" s="23">
         <v>7</v>
@@ -5662,8 +5671,8 @@
       <c r="AB45" s="23" t="s">
         <v>48</v>
       </c>
-      <c r="AC45" s="23" t="s">
-        <v>52</v>
+      <c r="AC45" s="19" t="s">
+        <v>60</v>
       </c>
       <c r="AD45" s="22" t="s">
         <v>51</v>
@@ -5690,7 +5699,7 @@
         <v>0</v>
       </c>
       <c r="AL45" s="23" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AM45" s="22" t="s">
         <v>50</v>
@@ -5795,7 +5804,7 @@
         <v>0</v>
       </c>
       <c r="AL46" s="19" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AM46" s="20" t="s"/>
     </row>
@@ -5898,7 +5907,7 @@
         <v>0</v>
       </c>
       <c r="AL47" s="19" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AM47" s="20" t="s"/>
     </row>
@@ -5950,7 +5959,7 @@
         <v>51</v>
       </c>
       <c r="U48" s="19" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="V48" s="22" t="s">
         <v>50</v>
@@ -5959,13 +5968,13 @@
         <v>54</v>
       </c>
       <c r="X48" s="19" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="Y48" s="19" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="Z48" s="19" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="AA48" s="19">
         <v>1</v>
@@ -6001,7 +6010,7 @@
         <v>0</v>
       </c>
       <c r="AL48" s="19" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AM48" s="20" t="s"/>
     </row>
@@ -6053,7 +6062,7 @@
         <v>51</v>
       </c>
       <c r="U49" s="19" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="V49" s="22" t="s">
         <v>50</v>
@@ -6062,13 +6071,13 @@
         <v>54</v>
       </c>
       <c r="X49" s="19" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="Y49" s="19" t="s">
         <v>54</v>
       </c>
       <c r="Z49" s="19" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="AA49" s="19">
         <v>2</v>
@@ -6104,7 +6113,7 @@
         <v>0</v>
       </c>
       <c r="AL49" s="19" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AM49" s="20" t="s"/>
     </row>
@@ -6115,7 +6124,7 @@
       <c r="D50" s="25" t="s"/>
       <c r="E50" s="25" t="s"/>
       <c r="F50" s="29" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="G50" s="23">
         <v>8</v>
@@ -6183,8 +6192,8 @@
       <c r="AB50" s="23" t="s">
         <v>48</v>
       </c>
-      <c r="AC50" s="23" t="s">
-        <v>52</v>
+      <c r="AC50" s="19" t="s">
+        <v>60</v>
       </c>
       <c r="AD50" s="22" t="s">
         <v>51</v>
@@ -6211,7 +6220,7 @@
         <v>0</v>
       </c>
       <c r="AL50" s="23" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AM50" s="22" t="s">
         <v>50</v>
@@ -6316,7 +6325,7 @@
         <v>0</v>
       </c>
       <c r="AL51" s="19" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AM51" s="20" t="s"/>
     </row>
@@ -6419,7 +6428,7 @@
         <v>0</v>
       </c>
       <c r="AL52" s="19" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AM52" s="20" t="s"/>
     </row>
@@ -6471,7 +6480,7 @@
         <v>51</v>
       </c>
       <c r="U53" s="28" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="V53" s="22" t="s">
         <v>51</v>
@@ -6486,7 +6495,7 @@
         <v>54</v>
       </c>
       <c r="Z53" s="28" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="AA53" s="28">
         <v>2</v>
@@ -6522,7 +6531,7 @@
         <v>0</v>
       </c>
       <c r="AL53" s="19" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AM53" s="20" t="s"/>
     </row>
@@ -6533,7 +6542,7 @@
       <c r="D54" s="25" t="s"/>
       <c r="E54" s="25" t="s"/>
       <c r="F54" s="40" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="G54" s="19">
         <v>9</v>
@@ -6602,7 +6611,7 @@
         <v>48</v>
       </c>
       <c r="AC54" s="19" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="AD54" s="20" t="s">
         <v>51</v>
@@ -6629,7 +6638,7 @@
         <v>0</v>
       </c>
       <c r="AL54" s="19" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AM54" s="20" t="s">
         <v>50</v>
@@ -6734,7 +6743,7 @@
         <v>0</v>
       </c>
       <c r="AL55" s="19" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AM55" s="20" t="s"/>
     </row>
@@ -6837,7 +6846,7 @@
         <v>0</v>
       </c>
       <c r="AL56" s="19" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AM56" s="20" t="s"/>
     </row>
@@ -6889,7 +6898,7 @@
         <v>51</v>
       </c>
       <c r="U57" s="19" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="V57" s="22" t="s">
         <v>51</v>
@@ -6901,10 +6910,10 @@
         <v>53</v>
       </c>
       <c r="Y57" s="19" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="Z57" s="19" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="AA57" s="19">
         <v>2</v>
@@ -6940,7 +6949,7 @@
         <v>0</v>
       </c>
       <c r="AL57" s="19" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AM57" s="20" t="s"/>
     </row>
@@ -6951,7 +6960,7 @@
       <c r="D58" s="25" t="s"/>
       <c r="E58" s="25" t="s"/>
       <c r="F58" s="40" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="G58" s="19">
         <v>10</v>
@@ -7020,7 +7029,7 @@
         <v>48</v>
       </c>
       <c r="AC58" s="19" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="AD58" s="20" t="s">
         <v>51</v>
@@ -7047,7 +7056,7 @@
         <v>0</v>
       </c>
       <c r="AL58" s="19" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AM58" s="20" t="s">
         <v>50</v>
@@ -7152,7 +7161,7 @@
         <v>0</v>
       </c>
       <c r="AL59" s="19" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AM59" s="20" t="s"/>
     </row>
@@ -7255,7 +7264,7 @@
         <v>0</v>
       </c>
       <c r="AL60" s="19" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AM60" s="20" t="s"/>
     </row>
@@ -7307,7 +7316,7 @@
         <v>51</v>
       </c>
       <c r="U61" s="19" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="V61" s="22" t="s">
         <v>51</v>
@@ -7319,10 +7328,10 @@
         <v>53</v>
       </c>
       <c r="Y61" s="19" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="Z61" s="19" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="AA61" s="19">
         <v>2</v>
@@ -7358,7 +7367,7 @@
         <v>0</v>
       </c>
       <c r="AL61" s="19" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AM61" s="20" t="s"/>
     </row>
@@ -7369,7 +7378,7 @@
       <c r="D62" s="25" t="s"/>
       <c r="E62" s="25" t="s"/>
       <c r="F62" s="29" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="G62" s="23">
         <v>11</v>
@@ -7437,8 +7446,8 @@
       <c r="AB62" s="23" t="s">
         <v>48</v>
       </c>
-      <c r="AC62" s="23" t="s">
-        <v>52</v>
+      <c r="AC62" s="19" t="s">
+        <v>60</v>
       </c>
       <c r="AD62" s="22" t="s">
         <v>51</v>
@@ -7465,7 +7474,7 @@
         <v>0</v>
       </c>
       <c r="AL62" s="23" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AM62" s="22" t="s">
         <v>50</v>
@@ -7570,7 +7579,7 @@
         <v>0</v>
       </c>
       <c r="AL63" s="19" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AM63" s="20" t="s"/>
     </row>
@@ -7673,7 +7682,7 @@
         <v>0</v>
       </c>
       <c r="AL64" s="19" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AM64" s="20" t="s"/>
     </row>
@@ -7725,7 +7734,7 @@
         <v>51</v>
       </c>
       <c r="U65" s="19" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="V65" s="22" t="s">
         <v>50</v>
@@ -7734,13 +7743,13 @@
         <v>54</v>
       </c>
       <c r="X65" s="19" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="Y65" s="19" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="Z65" s="19" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="AA65" s="19">
         <v>2</v>
@@ -7776,7 +7785,7 @@
         <v>0</v>
       </c>
       <c r="AL65" s="19" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AM65" s="20" t="s"/>
     </row>
@@ -7787,7 +7796,7 @@
       <c r="D66" s="25" t="s"/>
       <c r="E66" s="25" t="s"/>
       <c r="F66" s="33" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="G66" s="34">
         <v>12</v>
@@ -7855,8 +7864,8 @@
       <c r="AB66" s="34" t="s">
         <v>48</v>
       </c>
-      <c r="AC66" s="34" t="s">
-        <v>52</v>
+      <c r="AC66" s="19" t="s">
+        <v>60</v>
       </c>
       <c r="AD66" s="36" t="s">
         <v>51</v>
@@ -7883,7 +7892,7 @@
         <v>0</v>
       </c>
       <c r="AL66" s="34" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AM66" s="36" t="s">
         <v>50</v>
@@ -7988,7 +7997,7 @@
         <v>0</v>
       </c>
       <c r="AL67" s="19" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AM67" s="20" t="s"/>
     </row>
@@ -8091,7 +8100,7 @@
         <v>0</v>
       </c>
       <c r="AL68" s="19" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AM68" s="20" t="s"/>
     </row>
@@ -8143,7 +8152,7 @@
         <v>51</v>
       </c>
       <c r="U69" s="19" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="V69" s="22" t="s">
         <v>51</v>
@@ -8155,10 +8164,10 @@
         <v>53</v>
       </c>
       <c r="Y69" s="19" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="Z69" s="19" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="AA69" s="19">
         <v>0</v>
@@ -8194,7 +8203,7 @@
         <v>0</v>
       </c>
       <c r="AL69" s="19" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AM69" s="20" t="s"/>
     </row>
@@ -8205,7 +8214,7 @@
       <c r="D70" s="25" t="s"/>
       <c r="E70" s="25" t="s"/>
       <c r="F70" s="29" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="G70" s="19">
         <v>13</v>
@@ -8274,7 +8283,7 @@
         <v>48</v>
       </c>
       <c r="AC70" s="19" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="AD70" s="20" t="s">
         <v>51</v>
@@ -8301,7 +8310,7 @@
         <v>0</v>
       </c>
       <c r="AL70" s="19" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AM70" s="20" t="s">
         <v>50</v>
@@ -8406,7 +8415,7 @@
         <v>0</v>
       </c>
       <c r="AL71" s="19" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AM71" s="20" t="s"/>
     </row>
@@ -8509,7 +8518,7 @@
         <v>0</v>
       </c>
       <c r="AL72" s="19" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AM72" s="20" t="s"/>
     </row>
@@ -8561,7 +8570,7 @@
         <v>51</v>
       </c>
       <c r="U73" s="19" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="V73" s="22" t="s">
         <v>51</v>
@@ -8573,10 +8582,10 @@
         <v>53</v>
       </c>
       <c r="Y73" s="19" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="Z73" s="19" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="AA73" s="19">
         <v>0</v>
@@ -8612,7 +8621,7 @@
         <v>0</v>
       </c>
       <c r="AL73" s="19" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AM73" s="20" t="s"/>
     </row>
@@ -8623,7 +8632,7 @@
       <c r="D74" s="25" t="s"/>
       <c r="E74" s="25" t="s"/>
       <c r="F74" s="40" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="G74" s="19">
         <v>14</v>
@@ -8692,7 +8701,7 @@
         <v>48</v>
       </c>
       <c r="AC74" s="19" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="AD74" s="20" t="s">
         <v>51</v>
@@ -8719,7 +8728,7 @@
         <v>0</v>
       </c>
       <c r="AL74" s="19" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AM74" s="20" t="s">
         <v>50</v>
@@ -8824,7 +8833,7 @@
         <v>0</v>
       </c>
       <c r="AL75" s="19" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AM75" s="20" t="s"/>
     </row>
@@ -8927,7 +8936,7 @@
         <v>0</v>
       </c>
       <c r="AL76" s="19" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AM76" s="20" t="s"/>
     </row>
@@ -8979,7 +8988,7 @@
         <v>51</v>
       </c>
       <c r="U77" s="19" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="V77" s="22" t="s">
         <v>51</v>
@@ -8991,10 +9000,10 @@
         <v>53</v>
       </c>
       <c r="Y77" s="19" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="Z77" s="19" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="AA77" s="19">
         <v>0</v>
@@ -9030,7 +9039,7 @@
         <v>0</v>
       </c>
       <c r="AL77" s="19" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AM77" s="20" t="s"/>
     </row>
@@ -9041,7 +9050,7 @@
       <c r="D78" s="25" t="s"/>
       <c r="E78" s="25" t="s"/>
       <c r="F78" s="29" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="G78" s="23">
         <v>15</v>
@@ -9109,8 +9118,8 @@
       <c r="AB78" s="23" t="s">
         <v>48</v>
       </c>
-      <c r="AC78" s="23" t="s">
-        <v>52</v>
+      <c r="AC78" s="19" t="s">
+        <v>60</v>
       </c>
       <c r="AD78" s="22" t="s">
         <v>51</v>
@@ -9137,7 +9146,7 @@
         <v>0</v>
       </c>
       <c r="AL78" s="23" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AM78" s="22" t="s">
         <v>50</v>
@@ -9242,7 +9251,7 @@
         <v>0</v>
       </c>
       <c r="AL79" s="19" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AM79" s="20" t="s"/>
     </row>
@@ -9345,7 +9354,7 @@
         <v>0</v>
       </c>
       <c r="AL80" s="19" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AM80" s="20" t="s"/>
     </row>
@@ -9397,7 +9406,7 @@
         <v>51</v>
       </c>
       <c r="U81" s="19" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="V81" s="22" t="s">
         <v>50</v>
@@ -9406,13 +9415,13 @@
         <v>54</v>
       </c>
       <c r="X81" s="19" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="Y81" s="19" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="Z81" s="19" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="AA81" s="19">
         <v>0</v>
@@ -9448,7 +9457,7 @@
         <v>0</v>
       </c>
       <c r="AL81" s="19" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AM81" s="20" t="s"/>
     </row>
@@ -9500,7 +9509,7 @@
         <v>51</v>
       </c>
       <c r="U82" s="19" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="V82" s="22" t="s">
         <v>50</v>
@@ -9509,13 +9518,13 @@
         <v>54</v>
       </c>
       <c r="X82" s="19" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="Y82" s="19" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="Z82" s="19" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="AA82" s="19">
         <v>1</v>
@@ -9551,7 +9560,7 @@
         <v>0</v>
       </c>
       <c r="AL82" s="19" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AM82" s="20" t="s"/>
     </row>
@@ -9562,7 +9571,7 @@
       <c r="D83" s="25" t="s"/>
       <c r="E83" s="25" t="s"/>
       <c r="F83" s="29" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="G83" s="23">
         <v>16</v>
@@ -9630,8 +9639,8 @@
       <c r="AB83" s="23" t="s">
         <v>48</v>
       </c>
-      <c r="AC83" s="23" t="s">
-        <v>52</v>
+      <c r="AC83" s="19" t="s">
+        <v>60</v>
       </c>
       <c r="AD83" s="22" t="s">
         <v>51</v>
@@ -9658,7 +9667,7 @@
         <v>0</v>
       </c>
       <c r="AL83" s="23" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AM83" s="22" t="s">
         <v>50</v>
@@ -9763,7 +9772,7 @@
         <v>0</v>
       </c>
       <c r="AL84" s="19" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AM84" s="20" t="s"/>
     </row>
@@ -9866,7 +9875,7 @@
         <v>0</v>
       </c>
       <c r="AL85" s="19" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AM85" s="20" t="s"/>
     </row>
@@ -9918,7 +9927,7 @@
         <v>51</v>
       </c>
       <c r="U86" s="19" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="V86" s="22" t="s">
         <v>51</v>
@@ -9930,10 +9939,10 @@
         <v>53</v>
       </c>
       <c r="Y86" s="19" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="Z86" s="19" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="AA86" s="19">
         <v>1</v>
@@ -9969,7 +9978,7 @@
         <v>0</v>
       </c>
       <c r="AL86" s="19" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AM86" s="20" t="s"/>
     </row>
@@ -9980,7 +9989,7 @@
       <c r="D87" s="25" t="s"/>
       <c r="E87" s="25" t="s"/>
       <c r="F87" s="40" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="G87" s="19">
         <v>17</v>
@@ -10049,7 +10058,7 @@
         <v>48</v>
       </c>
       <c r="AC87" s="19" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="AD87" s="20" t="s">
         <v>51</v>
@@ -10076,7 +10085,7 @@
         <v>0</v>
       </c>
       <c r="AL87" s="19" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AM87" s="20" t="s">
         <v>50</v>
@@ -10181,7 +10190,7 @@
         <v>0</v>
       </c>
       <c r="AL88" s="19" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AM88" s="20" t="s"/>
     </row>
@@ -10284,7 +10293,7 @@
         <v>0</v>
       </c>
       <c r="AL89" s="19" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AM89" s="20" t="s"/>
     </row>
@@ -10336,7 +10345,7 @@
         <v>51</v>
       </c>
       <c r="U90" s="19" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="V90" s="22" t="s">
         <v>51</v>
@@ -10348,10 +10357,10 @@
         <v>53</v>
       </c>
       <c r="Y90" s="19" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="Z90" s="19" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="AA90" s="19">
         <v>1</v>
@@ -10387,7 +10396,7 @@
         <v>0</v>
       </c>
       <c r="AL90" s="19" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AM90" s="20" t="s"/>
     </row>
@@ -10398,7 +10407,7 @@
       <c r="D91" s="25" t="s"/>
       <c r="E91" s="25" t="s"/>
       <c r="F91" s="40" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="G91" s="19">
         <v>18</v>
@@ -10467,7 +10476,7 @@
         <v>48</v>
       </c>
       <c r="AC91" s="19" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="AD91" s="20" t="s">
         <v>51</v>
@@ -10494,7 +10503,7 @@
         <v>0</v>
       </c>
       <c r="AL91" s="19" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AM91" s="20" t="s">
         <v>50</v>
@@ -10599,7 +10608,7 @@
         <v>0</v>
       </c>
       <c r="AL92" s="19" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AM92" s="20" t="s"/>
     </row>
@@ -10702,7 +10711,7 @@
         <v>0</v>
       </c>
       <c r="AL93" s="19" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AM93" s="20" t="s"/>
     </row>
@@ -10754,7 +10763,7 @@
         <v>51</v>
       </c>
       <c r="U94" s="19" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="V94" s="22" t="s">
         <v>51</v>
@@ -10766,10 +10775,10 @@
         <v>53</v>
       </c>
       <c r="Y94" s="19" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="Z94" s="19" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="AA94" s="19">
         <v>1</v>
@@ -10805,7 +10814,7 @@
         <v>0</v>
       </c>
       <c r="AL94" s="19" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AM94" s="20" t="s"/>
     </row>
@@ -10816,7 +10825,7 @@
       <c r="D95" s="25" t="s"/>
       <c r="E95" s="25" t="s"/>
       <c r="F95" s="29" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="G95" s="23">
         <v>19</v>
@@ -10884,8 +10893,8 @@
       <c r="AB95" s="23" t="s">
         <v>48</v>
       </c>
-      <c r="AC95" s="23" t="s">
-        <v>52</v>
+      <c r="AC95" s="19" t="s">
+        <v>60</v>
       </c>
       <c r="AD95" s="22" t="s">
         <v>51</v>
@@ -10912,7 +10921,7 @@
         <v>0</v>
       </c>
       <c r="AL95" s="23" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AM95" s="22" t="s">
         <v>50</v>
@@ -11017,7 +11026,7 @@
         <v>0</v>
       </c>
       <c r="AL96" s="19" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AM96" s="20" t="s"/>
     </row>
@@ -11120,7 +11129,7 @@
         <v>0</v>
       </c>
       <c r="AL97" s="19" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AM97" s="20" t="s"/>
     </row>
@@ -11172,7 +11181,7 @@
         <v>51</v>
       </c>
       <c r="U98" s="19" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="V98" s="22" t="s">
         <v>50</v>
@@ -11181,13 +11190,13 @@
         <v>54</v>
       </c>
       <c r="X98" s="19" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="Y98" s="19" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="Z98" s="19" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="AA98" s="19">
         <v>1</v>
@@ -11223,7 +11232,7 @@
         <v>0</v>
       </c>
       <c r="AL98" s="19" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AM98" s="20" t="s"/>
     </row>
@@ -11275,7 +11284,7 @@
         <v>51</v>
       </c>
       <c r="U99" s="19" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="V99" s="22" t="s">
         <v>50</v>
@@ -11284,13 +11293,13 @@
         <v>54</v>
       </c>
       <c r="X99" s="19" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="Y99" s="19" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="Z99" s="19" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="AA99" s="19">
         <v>2</v>
@@ -11326,7 +11335,7 @@
         <v>0</v>
       </c>
       <c r="AL99" s="19" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AM99" s="20" t="s"/>
     </row>
@@ -11337,7 +11346,7 @@
       <c r="D100" s="25" t="s"/>
       <c r="E100" s="25" t="s"/>
       <c r="F100" s="29" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="G100" s="23">
         <v>20</v>
@@ -11405,8 +11414,8 @@
       <c r="AB100" s="23" t="s">
         <v>48</v>
       </c>
-      <c r="AC100" s="23" t="s">
-        <v>52</v>
+      <c r="AC100" s="19" t="s">
+        <v>60</v>
       </c>
       <c r="AD100" s="22" t="s">
         <v>51</v>
@@ -11433,7 +11442,7 @@
         <v>0</v>
       </c>
       <c r="AL100" s="23" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AM100" s="22" t="s">
         <v>50</v>
@@ -11538,7 +11547,7 @@
         <v>0</v>
       </c>
       <c r="AL101" s="19" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AM101" s="20" t="s"/>
     </row>
@@ -11641,7 +11650,7 @@
         <v>0</v>
       </c>
       <c r="AL102" s="19" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AM102" s="20" t="s"/>
     </row>
@@ -11693,7 +11702,7 @@
         <v>51</v>
       </c>
       <c r="U103" s="19" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="V103" s="22" t="s">
         <v>51</v>
@@ -11705,10 +11714,10 @@
         <v>53</v>
       </c>
       <c r="Y103" s="19" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="Z103" s="19" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="AA103" s="19">
         <v>2</v>
@@ -11744,7 +11753,7 @@
         <v>0</v>
       </c>
       <c r="AL103" s="19" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AM103" s="20" t="s"/>
     </row>
@@ -11755,7 +11764,7 @@
       <c r="D104" s="25" t="s"/>
       <c r="E104" s="25" t="s"/>
       <c r="F104" s="40" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="G104" s="19">
         <v>21</v>
@@ -11824,7 +11833,7 @@
         <v>48</v>
       </c>
       <c r="AC104" s="19" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="AD104" s="20" t="s">
         <v>51</v>
@@ -11851,7 +11860,7 @@
         <v>0</v>
       </c>
       <c r="AL104" s="19" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AM104" s="20" t="s">
         <v>50</v>
@@ -11956,7 +11965,7 @@
         <v>0</v>
       </c>
       <c r="AL105" s="19" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AM105" s="20" t="s"/>
     </row>
@@ -12059,7 +12068,7 @@
         <v>0</v>
       </c>
       <c r="AL106" s="19" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AM106" s="20" t="s"/>
     </row>
@@ -12111,7 +12120,7 @@
         <v>51</v>
       </c>
       <c r="U107" s="19" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="V107" s="22" t="s">
         <v>51</v>
@@ -12123,10 +12132,10 @@
         <v>53</v>
       </c>
       <c r="Y107" s="19" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="Z107" s="19" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="AA107" s="19">
         <v>2</v>
@@ -12162,7 +12171,7 @@
         <v>0</v>
       </c>
       <c r="AL107" s="19" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AM107" s="20" t="s"/>
     </row>
@@ -12173,7 +12182,7 @@
       <c r="D108" s="25" t="s"/>
       <c r="E108" s="25" t="s"/>
       <c r="F108" s="40" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="G108" s="19">
         <v>22</v>
@@ -12242,7 +12251,7 @@
         <v>48</v>
       </c>
       <c r="AC108" s="19" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="AD108" s="20" t="s">
         <v>51</v>
@@ -12269,7 +12278,7 @@
         <v>0</v>
       </c>
       <c r="AL108" s="19" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AM108" s="20" t="s">
         <v>50</v>
@@ -12374,7 +12383,7 @@
         <v>0</v>
       </c>
       <c r="AL109" s="19" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AM109" s="20" t="s"/>
     </row>
@@ -12477,7 +12486,7 @@
         <v>0</v>
       </c>
       <c r="AL110" s="19" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AM110" s="20" t="s"/>
     </row>
@@ -12529,7 +12538,7 @@
         <v>51</v>
       </c>
       <c r="U111" s="19" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="V111" s="22" t="s">
         <v>51</v>
@@ -12541,10 +12550,10 @@
         <v>53</v>
       </c>
       <c r="Y111" s="19" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="Z111" s="19" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="AA111" s="19">
         <v>2</v>
@@ -12580,7 +12589,7 @@
         <v>0</v>
       </c>
       <c r="AL111" s="19" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AM111" s="20" t="s"/>
     </row>
@@ -12591,7 +12600,7 @@
       <c r="D112" s="25" t="s"/>
       <c r="E112" s="25" t="s"/>
       <c r="F112" s="29" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="G112" s="23">
         <v>23</v>
@@ -12659,8 +12668,8 @@
       <c r="AB112" s="23" t="s">
         <v>48</v>
       </c>
-      <c r="AC112" s="23" t="s">
-        <v>52</v>
+      <c r="AC112" s="19" t="s">
+        <v>60</v>
       </c>
       <c r="AD112" s="22" t="s">
         <v>51</v>
@@ -12687,7 +12696,7 @@
         <v>0</v>
       </c>
       <c r="AL112" s="23" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AM112" s="22" t="s">
         <v>50</v>
@@ -12792,7 +12801,7 @@
         <v>0</v>
       </c>
       <c r="AL113" s="19" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AM113" s="20" t="s"/>
     </row>
@@ -12895,7 +12904,7 @@
         <v>0</v>
       </c>
       <c r="AL114" s="19" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AM114" s="20" t="s"/>
     </row>
@@ -12947,7 +12956,7 @@
         <v>51</v>
       </c>
       <c r="U115" s="14" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="V115" s="51" t="s">
         <v>50</v>
@@ -12956,13 +12965,13 @@
         <v>54</v>
       </c>
       <c r="X115" s="14" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="Y115" s="14" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="Z115" s="14" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="AA115" s="14">
         <v>2</v>
@@ -12998,7 +13007,7 @@
         <v>0</v>
       </c>
       <c r="AL115" s="14" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AM115" s="49" t="s"/>
     </row>
@@ -13007,19 +13016,19 @@
         <v>6</v>
       </c>
       <c r="B116" s="40" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="C116" s="40" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="D116" s="5" t="s">
         <v>53</v>
       </c>
       <c r="E116" s="5" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="F116" s="53" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="G116" s="19">
         <v>0</v>
@@ -13064,7 +13073,7 @@
         <v>51</v>
       </c>
       <c r="U116" s="55" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="V116" s="22" t="s">
         <v>51</v>
@@ -13079,7 +13088,7 @@
         <v>54</v>
       </c>
       <c r="Z116" s="55" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="AA116" s="23">
         <v>0</v>
@@ -13088,7 +13097,7 @@
         <v>48</v>
       </c>
       <c r="AC116" s="55" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="AD116" s="22" t="s">
         <v>51</v>
@@ -13115,7 +13124,7 @@
         <v>0</v>
       </c>
       <c r="AL116" s="23" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AM116" s="57" t="s"/>
     </row>
